--- a/projeto_invest_pro.xlsx
+++ b/projeto_invest_pro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nitro V\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FCDDE4F-DC00-48C3-9094-E2060DFFD6E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24276810-FC21-409B-B116-8C9140EDE5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="608" xr2:uid="{D63472A4-8300-4934-9C87-0EC792DCF89D}"/>
   </bookViews>
@@ -839,43 +839,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="3" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -918,6 +881,17 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -926,6 +900,32 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -973,10 +973,7 @@
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="dk1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -985,13 +982,8 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Carteira</a:t>
+              <a:t>Carteira recomendada</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> recomendada</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -1018,10 +1010,7 @@
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="dk1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -1180,17 +1169,15 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="bg2"/>
+                      <a:schemeClr val="dk1"/>
                     </a:solidFill>
-                    <a:latin typeface="Arial Narrow" panose="020B0606020202030204" pitchFamily="34" charset="0"/>
+                    <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
@@ -1329,10 +1316,7 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="dk1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -1349,16 +1333,14 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="lt1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="dk1"/>
       </a:solidFill>
-      <a:round/>
+      <a:prstDash val="solid"/>
+      <a:miter lim="800000"/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
@@ -1367,7 +1349,14 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="pt-BR"/>
     </a:p>
@@ -1403,10 +1392,7 @@
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="dk1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1415,13 +1401,8 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="pt-BR"/>
-              <a:t>Gráfico</a:t>
+              <a:t>Gráfico de cenários</a:t>
             </a:r>
-            <a:r>
-              <a:rPr lang="pt-BR" baseline="0"/>
-              <a:t> de cenários</a:t>
-            </a:r>
-            <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:rich>
       </c:tx>
@@ -1440,10 +1421,7 @@
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="dk1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -5160,10 +5138,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="dk1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -5219,10 +5194,7 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:schemeClr val="dk1"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -5261,10 +5233,7 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
+                <a:schemeClr val="dk1"/>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
@@ -5288,16 +5257,14 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="lt1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
+        <a:schemeClr val="dk1"/>
       </a:solidFill>
-      <a:round/>
+      <a:prstDash val="solid"/>
+      <a:miter lim="800000"/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
@@ -5306,7 +5273,14 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="dk1"/>
+          </a:solidFill>
+          <a:latin typeface="+mn-lt"/>
+          <a:ea typeface="+mn-ea"/>
+          <a:cs typeface="+mn-cs"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="pt-BR"/>
     </a:p>
@@ -13353,7 +13327,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67E754B3-F9E5-41E6-ADA4-8707897F047C}">
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.8" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.21875" style="1" customWidth="1"/>
@@ -13380,62 +13354,62 @@
     <row r="12" spans="2:4" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="2:4" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="14" spans="2:4" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="77" t="s">
+      <c r="B14" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="78"/>
-      <c r="D14" s="79"/>
+      <c r="C14" s="63"/>
+      <c r="D14" s="64"/>
     </row>
     <row r="15" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B15" s="65" t="s">
+      <c r="B15" s="79" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="66"/>
+      <c r="C15" s="80"/>
       <c r="D15" s="15">
         <v>4500</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B16" s="80" t="s">
+      <c r="B16" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="81"/>
+      <c r="C16" s="66"/>
       <c r="D16" s="24">
         <v>0.2</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B17" s="80" t="s">
+      <c r="B17" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="81"/>
+      <c r="C17" s="66"/>
       <c r="D17" s="16">
         <v>7</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B18" s="80" t="s">
+      <c r="B18" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="81"/>
+      <c r="C18" s="66"/>
       <c r="D18" s="17">
         <v>0.04</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B19" s="91" t="s">
+      <c r="B19" s="81" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="92"/>
+      <c r="C19" s="82"/>
       <c r="D19" s="25" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B20" s="65" t="s">
+      <c r="B20" s="79" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="66"/>
+      <c r="C20" s="80"/>
       <c r="D20" s="25" t="s">
         <v>32</v>
       </c>
@@ -13446,40 +13420,40 @@
       <c r="D21" s="25"/>
     </row>
     <row r="22" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B22" s="75" t="s">
+      <c r="B22" s="93" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="76"/>
+      <c r="C22" s="94"/>
       <c r="D22" s="26">
         <f>$D$15*$D$16</f>
         <v>900</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B23" s="93" t="s">
+      <c r="B23" s="83" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="94"/>
+      <c r="C23" s="84"/>
       <c r="D23" s="31" cm="1">
         <f t="array" ref="D23">SUMPRODUCT((AUXILIAR!$B$2:$B$19=D19) * (AUXILIAR!$D$2:$D$19) * (AUXILIAR!$E$2:$E$19))</f>
         <v>9.4249999999999994E-3</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="67" t="s">
+      <c r="B24" s="85" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="68"/>
+      <c r="C24" s="86"/>
       <c r="D24" s="31">
         <f>(1 + D18)^(1/12) - 1</f>
         <v>3.2737397821989145E-3</v>
       </c>
     </row>
     <row r="25" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="69" t="s">
+      <c r="B25" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="70"/>
+      <c r="C25" s="88"/>
       <c r="D25" s="27">
         <f>((1 + D23) / (1 + D24)) - 1</f>
         <v>6.1311883027421743E-3</v>
@@ -13487,37 +13461,37 @@
     </row>
     <row r="26" spans="2:5" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="2:5" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="62" t="s">
+      <c r="B27" s="76" t="s">
         <v>0</v>
       </c>
-      <c r="C27" s="63"/>
-      <c r="D27" s="64"/>
+      <c r="C27" s="77"/>
+      <c r="D27" s="78"/>
     </row>
     <row r="28" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B28" s="85" t="s">
+      <c r="B28" s="70" t="s">
         <v>25</v>
       </c>
-      <c r="C28" s="86"/>
+      <c r="C28" s="71"/>
       <c r="D28" s="29">
         <f>$D$22</f>
         <v>900</v>
       </c>
     </row>
     <row r="29" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="71" t="s">
+      <c r="B29" s="89" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="72"/>
+      <c r="C29" s="90"/>
       <c r="D29" s="34">
         <f>D17</f>
         <v>7</v>
       </c>
     </row>
     <row r="30" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B30" s="85" t="s">
+      <c r="B30" s="70" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="86"/>
+      <c r="C30" s="71"/>
       <c r="D30" s="26">
         <f>IF(D20="Sim", FV(D23, D17*12, -(D15*D16)), (D15*D16) * (D17*12))</f>
         <v>114491.20169890305</v>
@@ -13525,20 +13499,20 @@
       <c r="E30" s="2"/>
     </row>
     <row r="31" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B31" s="87" t="s">
+      <c r="B31" s="72" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="88"/>
+      <c r="C31" s="73"/>
       <c r="D31" s="32">
         <f>IF(D20="Sim", FV(D25, D17*12, -(D15*D16)), ((D15*D16) * (D17*12)) / (1+D18)^D17)</f>
         <v>98502.573030729138</v>
       </c>
     </row>
     <row r="32" spans="2:5" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="89" t="s">
+      <c r="B32" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="90"/>
+      <c r="C32" s="75"/>
       <c r="D32" s="30">
         <f>D30 * D23</f>
         <v>1079.0795760121612</v>
@@ -13546,11 +13520,11 @@
     </row>
     <row r="33" spans="1:12" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="34" spans="1:12" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="82" t="s">
+      <c r="B34" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="C34" s="83"/>
-      <c r="D34" s="84"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="69"/>
       <c r="E34" s="18"/>
       <c r="L34" s="3"/>
     </row>
@@ -13664,10 +13638,10 @@
     </row>
     <row r="42" spans="1:12" s="49" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="46"/>
-      <c r="B42" s="73" t="s">
+      <c r="B42" s="91" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="74"/>
+      <c r="C42" s="92"/>
       <c r="D42" s="54">
         <v>7</v>
       </c>
@@ -13780,11 +13754,11 @@
       <c r="D60" s="50"/>
     </row>
     <row r="61" spans="1:4" ht="29.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="62" t="s">
+      <c r="B61" s="76" t="s">
         <v>52</v>
       </c>
-      <c r="C61" s="63"/>
-      <c r="D61" s="64"/>
+      <c r="C61" s="77"/>
+      <c r="D61" s="78"/>
     </row>
     <row r="62" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B62" s="33" t="s">
@@ -13899,19 +13873,32 @@
     <row r="78" spans="2:4" x14ac:dyDescent="0.25"/>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25"/>
     <row r="80" spans="2:4" x14ac:dyDescent="0.25"/>
-    <row r="81" x14ac:dyDescent="0.25"/>
-    <row r="82" x14ac:dyDescent="0.25"/>
-    <row r="83" x14ac:dyDescent="0.25"/>
-    <row r="84" x14ac:dyDescent="0.25"/>
-    <row r="85" x14ac:dyDescent="0.25"/>
-    <row r="86" x14ac:dyDescent="0.25"/>
-    <row r="87" x14ac:dyDescent="0.25"/>
-    <row r="88" x14ac:dyDescent="0.25"/>
-    <row r="89" x14ac:dyDescent="0.25"/>
-    <row r="90" x14ac:dyDescent="0.25"/>
-    <row r="91" x14ac:dyDescent="0.25"/>
+    <row r="81" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="82" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="83" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="84" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="85" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="86" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="87" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="88" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="89" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="90" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="91" s="1" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="92" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="93" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="94" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="95" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="96" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="97" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B22:C22"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B17:C17"/>
@@ -13925,13 +13912,6 @@
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B22:C22"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D16" xr:uid="{B5BE23E5-C627-4DAC-A1FC-4C025CA7D03B}">
@@ -22240,6 +22220,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="851b35d3-0456-4d6a-bc2f-da927e91d158">
@@ -22248,15 +22237,6 @@
     <TaxCatchAll xmlns="19483571-f922-4e8e-9c1c-26f0a2252132" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22515,20 +22495,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C32110DE-3D77-470C-9CED-65521C30E3F6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54D0D6DD-E6DB-45C8-8F90-E314C090C085}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="851b35d3-0456-4d6a-bc2f-da927e91d158"/>
     <ds:schemaRef ds:uri="19483571-f922-4e8e-9c1c-26f0a2252132"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C32110DE-3D77-470C-9CED-65521C30E3F6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
